--- a/DAX_measures_and_user_defined_function.xlsx
+++ b/DAX_measures_and_user_defined_function.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Measures" sheetId="1" state="visible" r:id="rId3"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="501">
   <si>
     <t xml:space="preserve">Name</t>
   </si>
@@ -546,12 +546,6 @@
     <t xml:space="preserve">[Gross Margin Actual] - [Gross Margin Budget] </t>
   </si>
   <si>
-    <t xml:space="preserve">Gross Margin Variance %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIVIDE([Gross Margin Variance], [Gross Margin Budget])</t>
-  </si>
-  <si>
     <t xml:space="preserve">Total Revenue Variance Text</t>
   </si>
   <si>
@@ -594,7 +588,7 @@
     )</t>
   </si>
   <si>
-    <t xml:space="preserve">Gross Margin Variance Text</t>
+    <t xml:space="preserve">Gross Margin Variance Text (pp)</t>
   </si>
   <si>
     <t xml:space="preserve">
@@ -676,18 +670,29 @@
   </si>
   <si>
     <t xml:space="preserve">
-VAR IsRevenue = SELECTEDVALUE('Dim_Account'[AccountType]) = "Revenue"
+SUMX(
+    VALUES('Dim_Account'[Account]),
+    VAR IsRevenue =
+        CALCULATE(SELECTEDVALUE('Dim_Account'[AccountType])) = "Revenue"
+    RETURN
+        IF(IsRevenue, [Variance], -[Variance])
+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorable Variance %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+VAR BaseAmount =
+    SUMX(
+        VALUES('Dim_Account'[Account]),
+        VAR IsRevenue =
+            CALCULATE(SELECTEDVALUE('Dim_Account'[AccountType])) = "Revenue"
+        RETURN
+            IF(IsRevenue, [Budget Amount], -[Budget Amount])
+    )
 RETURN
-IF(IsRevenue, [Variance], -[Variance])</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Favorable Variance %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-VAR IsRevenue = SELECTEDVALUE('Dim_Account'[AccountType]) = "Revenue"
-RETURN
-IF(IsRevenue, [Variance %], -[Variance %])</t>
+    DIVIDE([Favorable Variance], ABS(BaseAmount))</t>
   </si>
   <si>
     <t xml:space="preserve">RnM Variance %</t>
@@ -1328,15 +1333,15 @@
   </si>
   <si>
     <t xml:space="preserve">
-VAR Actual_Unit_Price_Mar = 
+VAR Budget_Unit_Price_Mar =
     LOOKUPVALUE(
-        Actual_Drivers[DriverValue],
-        Actual_Drivers[Account], "Revenue",
-        Actual_Drivers[DriverMetric], "UnitPrice",
-        Actual_Drivers[Date], DATE(2025, 3, 1)
+        Budget_Drivers[DriverValue],
+        Budget_Drivers[Account], "Revenue",
+        Budget_Drivers[DriverMetric], "UnitPrice",
+        Budget_Drivers[Date], DATE(2025, 3, 1)
     )
 RETURN
-    Actual_Unit_Price_Mar * [Mar New Sales Units]</t>
+    Budget_Unit_Price_Mar * [Mar New Sales Units]</t>
   </si>
   <si>
     <t xml:space="preserve">Jan Bkd Repair</t>
@@ -1387,6 +1392,515 @@
   </si>
   <si>
     <t xml:space="preserve">[Capacity Utilization Variance] * 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Driver Sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUM(Forecast_Drivers[DriverValue])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCULATE([Forecast Driver Sum], Forecast_Drivers[Account] = "Revenue", Forecast_Drivers[DriverMetric] = "Quantity") </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUM(Fact_Forecast[Amount])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Revenue Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCULATE([Forecast Amount], Fact_Forecast[Account] = "Revenue")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast RM Quantity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCULATE([Forecast Driver Sum], Forecast_Drivers[Account] = "Raw Materials", Forecast_Drivers[DriverMetric] = "Quantity")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast RM TonsPerUnit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIVIDE([Forecast RM Quantity], [Forecast Units])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast RM Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCULATE([Forecast Amount], Fact_Forecast[Account] = "Raw Materials")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast RM Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIVIDE([Forecast RM Amount], [Forecast RM Quantity]) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast HoursPerUnit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCULATE(
+        SELECTEDVALUE(Forecast_Drivers[DriverValue]), 
+        Forecast_Drivers[Account] = "Direct Labor – Regular",
+        Forecast_Drivers[DriverMetric] = "HoursPerUnit"
+    )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Reg Hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCULATE([Forecast Driver Sum], Forecast_Drivers[Account] = "Direct Labor – Regular", Forecast_Drivers[DriverMetric] = "RegularHours") </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast OT Hours</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCULATE([Forecast Driver Sum], Forecast_Drivers[Account] = "Direct Labor – Overtime", Forecast_Drivers[DriverMetric] = "OvertimeHours")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast OT Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCULATE([Forecast Amount], Fact_Forecast[Account] = "Direct Labor – Overtime") </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast OT Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+VAR StdOTRate = 
+    CALCULATE(
+        SELECTEDVALUE(Forecast_Drivers[DriverValue]),
+        Forecast_Drivers[Account] = "Direct Labor – Overtime", 
+        Forecast_Drivers[DriverMetric] = "OvertimeRate"
+    )
+RETURN
+    IF(
+        ISBLANK([Forecast OT Hours]) || [Forecast OT Hours] = 0,
+        StdOTRate,
+        DIVIDE([Forecast OT Amount], [Forecast OT Hours])
+    )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Selling Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIVIDE([Forecast Revenue Amount], [Forecast Units])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT Labor Rate Variance Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMX(
+    VALUES('Dim_Date'[Month]),
+    [Forecast OT Hours] * ([Forecast OT Rate] - [Budget OT Rate])
+   )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast\Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Freight Truckload Shipments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCULATE([Forecast Driver Sum], Forecast_Drivers[Account] = "Inbound Freight", Forecast_Drivers[DriverMetric] = "Quantity")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Freight Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCULATE([Forecast Amount], Fact_Forecast[Account] = "Inbound Freight")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Freight Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIVIDE([Forecast Freight Amount], [Forecast Freight Truckload Shipments]) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Reg Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCULATE([Forecast Amount], Fact_Forecast[Account] = "Direct Labor – Regular") </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Reg Rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIVIDE([Forecast Reg Amount], [Forecast Reg Hours])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT Hours (Budget STD) Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMX(
+    VALUES('Dim_Date'[Month]),
+    MAX(0, [Forecast Units] * [Budget HoursPerUnit] - [Budget Reg Hours])
+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT Activity Variance Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMX(
+    VALUES('Dim_Date'[Month]),
+    ([OT Hours (Budget STD) Budget vs Forecast] - [Budget OT Hours]) * [Budget OT Rate] 
+    )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reg Labor Rate Variance Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMX(
+    VALUES('Dim_Date'[Month]),
+    [Forecast Reg Hours] * ([Forecast Reg Rate] - [Budget Reg Rate])
+    )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freight Activity Variance Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+SUMX(
+    VALUES('Dim_Date'[Month]),
+    VAR TruckloadAtForecastUnits = ROUNDUP([Forecast Units] * [Budget RM TonsPerUnit] / [Truck Capacity], 0)
+    VAR TruckloadAtBudgetUnits = ROUNDUP([Budget Units] * [Budget RM TonsPerUnit] / [Truck Capacity], 0)
+    RETURN
+        (TruckloadAtForecastUnits - TruckloadAtBudgetUnits) * [Budget Freight Rate]
+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freight Rate Variance Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMX(
+    VALUES('Dim_Date'[Month]),
+    [Forecast Freight Truckload Shipments] * ([Forecast Freight Rate] - [Budget Freight Rate])
+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM Activity Variance Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMX(
+    VALUES('Dim_Date'[Month]), 
+    ([Forecast Units] - [Budget Units]) * [Budget RM TonsPerUnit] * [Budget RM Price]
+    )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM Price Variance Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMX(
+    VALUES('Dim_Date'[Month]),
+    [Forecast Units] * [Forecast RM TonsPerUnit] * ([Forecast RM Price] - [Budget RM Price])
+    )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue Price Variance Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMX(
+    VALUES('Dim_Date'[Month]), 
+    [Forecast Units] * ([Forecast Selling Price] - [Budget Selling Price])
+    )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue Volume Variance Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMX(
+    VALUES('Dim_Date'[Month]), 
+    ([Forecast Units] - [Budget Units]) * [Budget Selling Price]
+    )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT Variance Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Forecast OT Amount] - [Budget OT Amount]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reg Variance Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Forecast Reg Amount] - [Budget Reg Amount] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freight Variance Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Forecast Freight Amount] - [Budget Freight Amount]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenue Variance Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Forecast Revenue Amount] - [Budget Revenue Amount]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM Variance Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Forecast RM Amount] - [Budget RM Amount]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast RnM Amount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCULATE([Forecast Amount], Fact_Forecast[Account] = "Repairs &amp; Maintenance")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RnM Variance Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Forecast RnM Amount] - [Budget RnM Amount] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Profit Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Total Revenue Forecast] - [Total COGS Forecast]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total COGS Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCULATE([Forecast Amount], Dim_Account[AccountType] = "Cost") </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Revenue Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CALCULATE([Forecast Amount], Dim_Account[AccountType] = "Revenue")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Profit Variance Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Gross Profit Forecast] - [Gross Profit Budget]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RM Usage Variance Forecast vs Actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMX(
+    VALUES('Dim_Date'[Month]),
+    [Actual Units] * ([Actual RM TonsPerUnit] - [Forecast RM TonsPerUnit]) * [Forecast RM Price]
+    )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast\Forecast vs Actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freight RM Qty per Unit Impact Forecast vs Actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+SUMX(
+    VALUES('Dim_Date'[Month]),
+    VAR TruckloadAtActualSQ = ROUNDUP([Actual Units] * [Actual RM TonsPerUnit] / [Truck Capacity], 0)
+    VAR TruckloadAtForecastSQ = ROUNDUP([Actual Units] * [Forecast RM TonsPerUnit] / [Truck Capacity], 0)
+    RETURN
+        (TruckloadAtActualSQ - TruckloadAtForecastSQ) * [Forecast Freight Rate]
+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT Hours (Forecast STD) Forecast vs Actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMX(
+    VALUES('Dim_Date'[Month]),
+    MAX(0, [Actual Units] * [Forecast HoursPerUnit] - [Forecast Reg Hours])
+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT Labor Efficiency Variance Forecast vs Actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUMX(
+    VALUES('Dim_Date'[Month]),
+    ( [Actual OT Hours] - [OT Hours (Forecast STD) Forecast vs Actual] ) * [Forecast OT Rate]
+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Profit Variance Forecast vs Actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Gross Profit Actual] - [Gross Profit Forecast]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Profit Variance % Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIVIDE([Gross Profit Variance Budget vs Forecast], [Gross Profit Budget])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Profit Variance % Forecast vs Actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIVIDE([Gross Profit Variance Forecast vs Actual], [Gross Profit Forecast])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Margin Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIVIDE([Gross Profit Forecast], [Total Revenue Forecast])  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Margin Variance Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Gross Margin Forecast] - [Gross Margin Budget] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Margin Variance (pp) Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Gross Margin Variance Budget vs Forecast] * 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Margin Variance Forecast vs Actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Gross Margin Actual] - [Gross Margin Forecast] </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Margin Variance (pp) Forecast vs Actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">[Gross Margin Variance Forecast vs Actual] * 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Margin Variance Text (pp) Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+VAR VarPct = [Gross Margin Variance Budget vs Forecast]
+RETURN
+    SWITCH(
+        TRUE(),
+        VarPct = 0, " " &amp; FORMAT( VarPct * 100, "0.00" ) &amp; " pp",
+        VarPct &gt; 0, "▲ +" &amp; FORMAT( VarPct * 100, "0.00" ) &amp; " pp",
+        "▼ -" &amp; FORMAT( ABS( VarPct * 100 ), "0.00" ) &amp; " pp"
+    )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Margin Variance Text (pp) Forecast vs Actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+VAR VarPct = [Gross Margin Variance Forecast vs Actual]
+RETURN
+    SWITCH(
+        TRUE(),
+        VarPct = 0, " " &amp; FORMAT( VarPct * 100, "0.00" ) &amp; " pp",
+        VarPct &gt; 0, "▲ +" &amp; FORMAT( VarPct * 100, "0.00" ) &amp; " pp",
+        "▼ -" &amp; FORMAT( ABS( VarPct * 100 ), "0.00" ) &amp; " pp"
+    )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Profit Variance Text Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+VAR VarPct = [Gross Profit Variance % Budget vs Forecast]
+RETURN
+    SWITCH(
+        TRUE(),
+        VarPct = 0, " " &amp; FORMAT( VarPct, "0.00%" ),
+        VarPct &gt; 0, "▲ +" &amp; FORMAT( VarPct, "0.00%" ),
+        "▼ -" &amp; FORMAT( ABS( VarPct ), "0.00%" )
+    )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Profit Variance Text Forecast vs Actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+VAR VarPct = [Gross Profit Variance % Forecast vs Actual]
+RETURN
+    SWITCH(
+        TRUE(),
+        VarPct = 0, " " &amp; FORMAT( VarPct, "0.00%" ),
+        VarPct &gt; 0, "▲ +" &amp; FORMAT( VarPct, "0.00%" ),
+        "▼ -" &amp; FORMAT( ABS( VarPct ), "0.00%" )
+    )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Captured %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+DIVIDE([Gross Profit Variance Budget vs Forecast], [Gross Profit Variance])</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Captured Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+VAR ForecastShortfall = -[Gross Profit Variance Budget vs Forecast]
+VAR ActualShortfall   = -[Gross Profit Variance]
+RETURN
+"The 9+3 forecast anticipated a €" &amp; FORMAT(ForecastShortfall / 1000, "#,##0") &amp;
+"K gross profit shortfall vs Budget, equal to " &amp; FORMAT([Forecast Captured %], "0%") &amp;
+" of the €" &amp; FORMAT(ActualShortfall / 1000, "#,##0") &amp; "K actual shortfall vs Budget. The remaining €" &amp; FORMAT((ActualShortfall-ForecastShortfall) / 1000, "#,##0") &amp; "K came from two events not known at the time of the forecast (Nov's higher hours per unit and Dec's raw material quality issue) and normal fluctuations."</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Profit Variance Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+VAR CheckSum = [Gross Profit Variance Budget vs Forecast] + [Gross Profit Variance Forecast vs Actual]
+RETURN IF(ABS(CheckSum - [Gross Profit Variance]) &lt; 1, "Correct", "Wrong")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Profit Variance Budget vs Forecast Jan-Sep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+CALCULATE(
+    [Gross Profit Variance Budget vs Forecast],
+    Dim_Date[Month] IN {"Jan","Feb","Mar","Apr","May","Jun","Jul","Aug","Sep"}
+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Profit Variance Budget vs Forecast Oct-Dec</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+CALCULATE(
+    [Gross Profit Variance Budget vs Forecast],
+    Dim_Date[Month] IN {"Oct","Nov","Dec"}
+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross Profit Forecast Timing Check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+VAR CheckSum = [Gross Profit Variance Budget vs Forecast Jan-Sep] + [Gross Profit Variance Budget vs Forecast Oct-Dec]
+RETURN IF(ABS(CheckSum - [Gross Profit Variance Budget vs Forecast]) &lt; 1, "Correct", "Wrong")</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forecast Timing Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+VAR JanSep = -[Gross Profit Variance Budget vs Forecast Jan-Sep]
+VAR OctDec = -[Gross Profit Variance Budget vs Forecast Oct-Dec]
+VAR Total  = -[Gross Profit Variance Budget vs Forecast]
+RETURN
+"At the Sep close, " &amp; FORMAT(DIVIDE(JanSep, Total), "0%") &amp;
+" of the forecast full-year gross profit shortfall vs Budget (€" &amp; FORMAT(JanSep / 1000, "#,##0") &amp; "K of €" &amp; FORMAT(Total / 1000, "#,##0") &amp;
+"K) had already occurred; the remaining " &amp; FORMAT(DIVIDE(OctDec, Total), "0%") &amp;
+" (€" &amp; FORMAT(OctDec / 1000, "#,##0") &amp; "K) was still expected in Oct–Dec, mainly from the Nov–Dec raw material price increase."</t>
   </si>
   <si>
     <t xml:space="preserve">RnM Bridge Value</t>
@@ -1413,18 +1927,6 @@
   </si>
   <si>
     <t xml:space="preserve">VAR Category = SELECTEDVALUE('Bridge Revenue'[CategoryKey]) 
-VAR Actual_Unit_Price_Jan = LOOKUPVALUE(
-    Actual_Drivers[DriverValue],
-    Actual_Drivers[Account], "Revenue",
-    Actual_Drivers[DriverMetric], "UnitPrice",
-    Actual_Drivers[Date], DATE (2025, 1, 1)
-    ) 
-VAR Actual_Unit_Price_Mar = LOOKUPVALUE(
-    Actual_Drivers[DriverValue],
-    Actual_Drivers[Account], "Revenue",
-    Actual_Drivers[DriverMetric], "UnitPrice",
-    Actual_Drivers[Date], DATE (2025, 3, 1)
-    )
 RETURN
 CALCULATE ( 
 SWITCH(
@@ -1459,7 +1961,7 @@
         "Mar", [Mar New Freight Activity Variance],
         "Other Activity Variance",
             [Freight Activity Variance] - [Jan Bkd Freight Activity Variance] - [Mar New Freight Activity Variance],
-        "Dec", CALCULATE([Freight RM Qty per Unit Impact], Dim_Date[Month]="Dec"),
+        "Dec", [Freight RM Qty per Unit Impact],
         "Rate Variance", [Freight Rate Variance],
         BLANK()
     ),
@@ -1530,7 +2032,7 @@
   </si>
   <si>
     <t xml:space="preserve">
-VAR Category = SELECTEDVALUE('Bridge Account'[CategoryKey])
+VAR Category = SELECTEDVALUE('Bridge Account - Budget vs Actual'[CategoryKey])
 RETURN
     SWITCH(
         Category,
@@ -1550,7 +2052,7 @@
   </si>
   <si>
     <t xml:space="preserve">
-VAR Category = SELECTEDVALUE('Bridge Event'[CategoryKey])
+VAR Category = SELECTEDVALUE('Bridge Event - Budget vs Actual'[CategoryKey])
 RETURN
 CALCULATE(
     VAR Jan_Bkd = 
@@ -1561,7 +2063,6 @@
         -[OT Labor Rate Variance] - [Reg Labor Rate Variance]
     VAR RM_Usage 
         = -[RM Usage Variance] - [Freight RM Qty per Unit Impact]
-    VAR Gross_Variance = [Revenue Variance] - [RM Variance] - [Reg Variance] - [OT Variance] - [Freight Variance] - [RnM Variance]
     RETURN
     SWITCH(
         Category,
@@ -1575,7 +2076,60 @@
         "Nov: Hours per Unit Increase", -[OT Labor Efficiency Variance],
         "Dec: Raw Material Quantity per Unit Increase", RM_Usage,
         "Nov-Dec: RM Price Increase", -[RM Price Variance],
-        "Impact of Normal Fluctuations", Gross_Variance  - Jan_Bkd - Mar_New - Labor_Rate_Increase - [Revenue Price Variance] - -[Aug Reduced Repair] - -[Freight Rate Variance] - -[OT Labor Efficiency Variance] - RM_Usage - -[RM Price Variance],
+        "Impact of Normal Fluctuations", [Gross Profit Variance]  - Jan_Bkd - Mar_New - Labor_Rate_Increase - [Revenue Price Variance] - -[Aug Reduced Repair] - -[Freight Rate Variance] - -[OT Labor Efficiency Variance] - RM_Usage - -[RM Price Variance],
+        BLANK()
+    ),
+    ALL('Dim_Date')
+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GP Event Bridge Value Budget vs Forecast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+VAR Category = SELECTEDVALUE('Event Bridge - Budget vs Forecast'[CategoryKey])
+RETURN
+CALCULATE(
+    VAR Jan_Bkd = 
+        [Jan Bkd Revenue] - [Jan Bkd RM Activity Variance] - [Jan Bkd Freight Activity Variance] - [Jan Bkd Repair]
+    VAR Mar_New = 
+        [Mar New Revenue] - [Mar New RM Activity Variance] - [Mar New Freight Activity Variance] - [Mar OT Activity Variance]
+    VAR Labor_Rate_Increase = 
+        -[OT Labor Rate Variance Budget vs Forecast] - [Reg Labor Rate Variance Budget vs Forecast]
+    RETURN
+    SWITCH(
+        Category,
+        "Budget", [Gross Profit Budget],
+        "Jan: Unplanned Breakdown", Jan_Bkd,
+        "Mar: New Order", Mar_New,
+        "May-Dec: Labor Rate Increase", Labor_Rate_Increase,
+        "Jul-Dec: Selling Price Increase", [Revenue Price Variance Budget vs Forecast],
+        "Aug: Repair Brought Forward to Jan", -[Aug Reduced Repair],
+        "Sep-Dec: Freight Rate Increase", -[Freight Rate Variance Budget vs Forecast],
+        "Nov-Dec: RM Price Increase", -[RM Price Variance Budget vs Forecast],
+        "Impact of Normal Fluctuations", [Gross Profit Variance Budget vs Forecast]  - Jan_Bkd - Mar_New - Labor_Rate_Increase - [Revenue Price Variance Budget vs Forecast] - -[Aug Reduced Repair] - -[Freight Rate Variance Budget vs Forecast] - -[RM Price Variance Budget vs Forecast],
+        BLANK()
+    ),
+    ALL('Dim_Date')
+)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GP Event Bridge Value Forecast vs Actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+VAR Category = SELECTEDVALUE('Event Bridge - Forecast vs Actual'[CategoryKey])
+RETURN
+CALCULATE(
+    VAR RM_Usage 
+        = -[RM Usage Variance Forecast vs Actual] - [Freight RM Qty per Unit Impact Forecast vs Actual]
+    RETURN
+    SWITCH(
+        Category,
+        "Forecast", [Gross Profit Forecast],
+        "Nov: Hours per Unit Increase", -[OT Labor Efficiency Variance Forecast vs Actual],
+        "Dec: Raw Material Quantity per Unit Increase", RM_Usage,
+        "Impact of Normal Fluctuations", [Gross Profit Variance Forecast vs Actual] - RM_Usage - -[OT Labor Efficiency Variance Forecast vs Actual],
         BLANK()
     ),
     ALL('Dim_Date')
@@ -1601,11 +2155,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1634,12 +2189,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -1705,7 +2254,7 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1929,13 +2478,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D174"/>
+  <dimension ref="A1:D238"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="147.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="20.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24.77"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2030,7 +2579,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="163" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>20</v>
       </c>
@@ -2041,7 +2590,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="174.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>22</v>
       </c>
@@ -2177,7 +2726,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="197.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
         <v>45</v>
       </c>
@@ -2188,7 +2737,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="220.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
         <v>47</v>
       </c>
@@ -2199,7 +2748,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="209" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
         <v>49</v>
       </c>
@@ -2335,7 +2884,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="554.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="94" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
         <v>73</v>
       </c>
@@ -2346,7 +2895,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="209" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
         <v>75</v>
       </c>
@@ -2521,7 +3070,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="600.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="151.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
         <v>106</v>
       </c>
@@ -2532,7 +3081,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="577.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="151.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
         <v>108</v>
       </c>
@@ -2546,7 +3095,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="174.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
         <v>110</v>
       </c>
@@ -2568,7 +3117,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="186" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
         <v>114</v>
       </c>
@@ -2579,7 +3128,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="163" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
         <v>116</v>
       </c>
@@ -2813,21 +3362,18 @@
         <v>122</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="B71" s="0" t="s">
+      <c r="B71" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="C71" s="0" t="s">
-        <v>137</v>
       </c>
       <c r="D71" s="0" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="370.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
         <v>156</v>
       </c>
@@ -2838,7 +3384,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="370.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
         <v>158</v>
       </c>
@@ -2849,7 +3395,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="370.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
         <v>160</v>
       </c>
@@ -2860,15 +3406,15 @@
         <v>122</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="416.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="0" t="s">
         <v>162</v>
       </c>
-      <c r="B75" s="2" t="s">
+      <c r="B75" s="0" t="s">
         <v>163</v>
       </c>
       <c r="D75" s="0" t="s">
-        <v>122</v>
+        <v>12</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2878,29 +3424,29 @@
       <c r="B76" s="0" t="s">
         <v>165</v>
       </c>
+      <c r="C76" s="0" t="s">
+        <v>137</v>
+      </c>
       <c r="D76" s="0" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="B77" s="0" t="s">
+      <c r="B77" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="C77" s="0" t="s">
-        <v>137</v>
       </c>
       <c r="D77" s="0" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="359" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="0" t="s">
         <v>168</v>
       </c>
-      <c r="B78" s="2" t="s">
+      <c r="B78" s="0" t="s">
         <v>169</v>
       </c>
       <c r="D78" s="0" t="s">
@@ -2914,33 +3460,30 @@
       <c r="B79" s="0" t="s">
         <v>171</v>
       </c>
+      <c r="C79" s="0" t="s">
+        <v>137</v>
+      </c>
       <c r="D79" s="0" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B80" s="0" t="s">
+      <c r="B80" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="C80" s="0" t="s">
-        <v>137</v>
       </c>
       <c r="D80" s="0" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="382" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="0" t="s">
         <v>174</v>
       </c>
-      <c r="B81" s="2" t="s">
+      <c r="B81" s="0" t="s">
         <v>175</v>
-      </c>
-      <c r="D81" s="0" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2950,35 +3493,41 @@
       <c r="B82" s="0" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C82" s="0" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="94" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="B83" s="0" t="s">
+      <c r="B83" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C83" s="0" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="220.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="84" customFormat="false" ht="128.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
         <v>180</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="85" customFormat="false" ht="220.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C84" s="0" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="0" t="s">
         <v>182</v>
       </c>
-      <c r="B85" s="2" t="s">
+      <c r="B85" s="0" t="s">
         <v>183</v>
       </c>
       <c r="C85" s="0" t="s">
         <v>137</v>
+      </c>
+      <c r="D85" s="0" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2992,7 +3541,7 @@
         <v>137</v>
       </c>
       <c r="D86" s="0" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3002,9 +3551,6 @@
       <c r="B87" s="0" t="s">
         <v>187</v>
       </c>
-      <c r="C87" s="0" t="s">
-        <v>137</v>
-      </c>
       <c r="D87" s="0" t="s">
         <v>12</v>
       </c>
@@ -3016,9 +3562,6 @@
       <c r="B88" s="0" t="s">
         <v>189</v>
       </c>
-      <c r="D88" s="0" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="0" t="s">
@@ -3027,6 +3570,12 @@
       <c r="B89" s="0" t="s">
         <v>191</v>
       </c>
+      <c r="C89" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="D89" s="0" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="0" t="s">
@@ -3039,7 +3588,7 @@
         <v>137</v>
       </c>
       <c r="D90" s="0" t="s">
-        <v>12</v>
+        <v>55</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3053,7 +3602,7 @@
         <v>137</v>
       </c>
       <c r="D91" s="0" t="s">
-        <v>55</v>
+        <v>12</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3063,11 +3612,8 @@
       <c r="B92" s="0" t="s">
         <v>197</v>
       </c>
-      <c r="C92" s="0" t="s">
-        <v>137</v>
-      </c>
       <c r="D92" s="0" t="s">
-        <v>12</v>
+        <v>62</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3077,6 +3623,9 @@
       <c r="B93" s="0" t="s">
         <v>199</v>
       </c>
+      <c r="C93" s="0" t="s">
+        <v>137</v>
+      </c>
       <c r="D93" s="0" t="s">
         <v>62</v>
       </c>
@@ -3088,11 +3637,8 @@
       <c r="B94" s="0" t="s">
         <v>201</v>
       </c>
-      <c r="C94" s="0" t="s">
-        <v>137</v>
-      </c>
       <c r="D94" s="0" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3102,6 +3648,9 @@
       <c r="B95" s="0" t="s">
         <v>203</v>
       </c>
+      <c r="C95" s="0" t="s">
+        <v>137</v>
+      </c>
       <c r="D95" s="0" t="s">
         <v>91</v>
       </c>
@@ -3113,11 +3662,8 @@
       <c r="B96" s="0" t="s">
         <v>205</v>
       </c>
-      <c r="C96" s="0" t="s">
-        <v>137</v>
-      </c>
       <c r="D96" s="0" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3127,6 +3673,9 @@
       <c r="B97" s="0" t="s">
         <v>207</v>
       </c>
+      <c r="C97" s="0" t="s">
+        <v>137</v>
+      </c>
       <c r="D97" s="0" t="s">
         <v>81</v>
       </c>
@@ -3138,11 +3687,8 @@
       <c r="B98" s="0" t="s">
         <v>209</v>
       </c>
-      <c r="C98" s="0" t="s">
-        <v>137</v>
-      </c>
       <c r="D98" s="0" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3152,6 +3698,9 @@
       <c r="B99" s="0" t="s">
         <v>211</v>
       </c>
+      <c r="C99" s="0" t="s">
+        <v>137</v>
+      </c>
       <c r="D99" s="0" t="s">
         <v>30</v>
       </c>
@@ -3163,11 +3712,8 @@
       <c r="B100" s="0" t="s">
         <v>213</v>
       </c>
-      <c r="C100" s="0" t="s">
-        <v>137</v>
-      </c>
       <c r="D100" s="0" t="s">
-        <v>30</v>
+        <v>62</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3177,6 +3723,9 @@
       <c r="B101" s="0" t="s">
         <v>215</v>
       </c>
+      <c r="C101" s="0" t="s">
+        <v>137</v>
+      </c>
       <c r="D101" s="0" t="s">
         <v>62</v>
       </c>
@@ -3188,11 +3737,8 @@
       <c r="B102" s="0" t="s">
         <v>217</v>
       </c>
-      <c r="C102" s="0" t="s">
-        <v>137</v>
-      </c>
       <c r="D102" s="0" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3202,6 +3748,9 @@
       <c r="B103" s="0" t="s">
         <v>219</v>
       </c>
+      <c r="C103" s="0" t="s">
+        <v>137</v>
+      </c>
       <c r="D103" s="0" t="s">
         <v>30</v>
       </c>
@@ -3213,11 +3762,8 @@
       <c r="B104" s="0" t="s">
         <v>221</v>
       </c>
-      <c r="C104" s="0" t="s">
-        <v>137</v>
-      </c>
       <c r="D104" s="0" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3227,6 +3773,9 @@
       <c r="B105" s="0" t="s">
         <v>223</v>
       </c>
+      <c r="C105" s="0" t="s">
+        <v>137</v>
+      </c>
       <c r="D105" s="0" t="s">
         <v>81</v>
       </c>
@@ -3238,11 +3787,8 @@
       <c r="B106" s="0" t="s">
         <v>225</v>
       </c>
-      <c r="C106" s="0" t="s">
-        <v>137</v>
-      </c>
       <c r="D106" s="0" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3252,6 +3798,9 @@
       <c r="B107" s="0" t="s">
         <v>227</v>
       </c>
+      <c r="C107" s="0" t="s">
+        <v>137</v>
+      </c>
       <c r="D107" s="0" t="s">
         <v>91</v>
       </c>
@@ -3267,7 +3816,7 @@
         <v>137</v>
       </c>
       <c r="D108" s="0" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3295,7 +3844,7 @@
         <v>137</v>
       </c>
       <c r="D110" s="0" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3323,7 +3872,7 @@
         <v>137</v>
       </c>
       <c r="D112" s="0" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3351,7 +3900,7 @@
         <v>137</v>
       </c>
       <c r="D114" s="0" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3368,43 +3917,40 @@
         <v>91</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="71" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
         <v>244</v>
       </c>
-      <c r="B116" s="0" t="s">
+      <c r="B116" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="C116" s="0" t="s">
-        <v>137</v>
-      </c>
       <c r="D116" s="0" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="289.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="71" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
+        <v>247</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D117" s="0" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="71" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="0" t="s">
+        <v>250</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="D118" s="0" t="s">
         <v>246</v>
       </c>
-      <c r="B117" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="D117" s="0" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="118" customFormat="false" ht="289.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="0" t="s">
-        <v>249</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="D118" s="0" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="324" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="119" customFormat="false" ht="71" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
         <v>252</v>
       </c>
@@ -3412,10 +3958,10 @@
         <v>253</v>
       </c>
       <c r="D119" s="0" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="324" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
         <v>254</v>
       </c>
@@ -3423,21 +3969,24 @@
         <v>255</v>
       </c>
       <c r="D120" s="0" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="151.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="71" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
         <v>256</v>
       </c>
       <c r="B121" s="2" t="s">
         <v>257</v>
       </c>
+      <c r="C121" s="0" t="s">
+        <v>15</v>
+      </c>
       <c r="D121" s="0" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="312.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="71" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
         <v>258</v>
       </c>
@@ -3448,21 +3997,18 @@
         <v>15</v>
       </c>
       <c r="D122" s="0" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="312.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="0" t="s">
         <v>260</v>
       </c>
-      <c r="B123" s="2" t="s">
+      <c r="B123" s="0" t="s">
         <v>261</v>
       </c>
-      <c r="C123" s="0" t="s">
-        <v>15</v>
-      </c>
       <c r="D123" s="0" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3473,7 +4019,7 @@
         <v>263</v>
       </c>
       <c r="D124" s="0" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3484,7 +4030,7 @@
         <v>265</v>
       </c>
       <c r="D125" s="0" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3495,21 +4041,21 @@
         <v>267</v>
       </c>
       <c r="D126" s="0" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="127" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="71" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
         <v>268</v>
       </c>
-      <c r="B127" s="0" t="s">
+      <c r="B127" s="2" t="s">
         <v>269</v>
       </c>
       <c r="D127" s="0" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="324" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="71" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="s">
         <v>270</v>
       </c>
@@ -3517,10 +4063,10 @@
         <v>271</v>
       </c>
       <c r="D128" s="0" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="324" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="s">
         <v>272</v>
       </c>
@@ -3528,10 +4074,10 @@
         <v>273</v>
       </c>
       <c r="D129" s="0" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="819" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
         <v>274</v>
       </c>
@@ -3539,35 +4085,35 @@
         <v>275</v>
       </c>
       <c r="D130" s="0" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="131" customFormat="false" ht="266.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="0" t="s">
+        <v>277</v>
+      </c>
+      <c r="B131" s="0" t="s">
+        <v>278</v>
+      </c>
+      <c r="C131" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="D131" s="0" t="s">
         <v>276</v>
       </c>
-      <c r="B131" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="D131" s="0" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="132" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
         <v>279</v>
       </c>
-      <c r="B132" s="0" t="s">
+      <c r="B132" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="C132" s="0" t="s">
-        <v>137</v>
-      </c>
       <c r="D132" s="0" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="266.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="151.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
         <v>281</v>
       </c>
@@ -3575,10 +4121,10 @@
         <v>282</v>
       </c>
       <c r="D133" s="0" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="600.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="140" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
         <v>283</v>
       </c>
@@ -3586,18 +4132,21 @@
         <v>284</v>
       </c>
       <c r="D134" s="0" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="589" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="0" t="s">
         <v>285</v>
       </c>
-      <c r="B135" s="2" t="s">
+      <c r="B135" s="0" t="s">
         <v>286</v>
       </c>
+      <c r="C135" s="0" t="s">
+        <v>137</v>
+      </c>
       <c r="D135" s="0" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3611,24 +4160,21 @@
         <v>137</v>
       </c>
       <c r="D136" s="0" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="s">
         <v>289</v>
       </c>
-      <c r="B137" s="0" t="s">
+      <c r="B137" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="C137" s="0" t="s">
-        <v>137</v>
-      </c>
       <c r="D137" s="0" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="186" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
         <v>291</v>
       </c>
@@ -3639,7 +4185,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="197.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="94" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
         <v>293</v>
       </c>
@@ -3647,14 +4193,14 @@
         <v>294</v>
       </c>
       <c r="D139" s="0" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="554.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="0" t="s">
         <v>295</v>
       </c>
-      <c r="B140" s="2" t="s">
+      <c r="B140" s="0" t="s">
         <v>296</v>
       </c>
       <c r="D140" s="0" t="s">
@@ -3672,18 +4218,18 @@
         <v>62</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
         <v>299</v>
       </c>
-      <c r="B142" s="0" t="s">
+      <c r="B142" s="2" t="s">
         <v>300</v>
       </c>
       <c r="D142" s="0" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="370.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
         <v>301</v>
       </c>
@@ -3694,15 +4240,15 @@
         <v>62</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="370.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="0" t="s">
         <v>303</v>
       </c>
-      <c r="B144" s="2" t="s">
+      <c r="B144" s="0" t="s">
         <v>304</v>
       </c>
       <c r="D144" s="0" t="s">
-        <v>62</v>
+        <v>30</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3716,22 +4262,22 @@
         <v>30</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
         <v>307</v>
       </c>
-      <c r="B146" s="0" t="s">
+      <c r="B146" s="2" t="s">
         <v>308</v>
       </c>
       <c r="D146" s="0" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="370.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="0" t="s">
         <v>309</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="B147" s="0" t="s">
         <v>310</v>
       </c>
       <c r="D147" s="0" t="s">
@@ -3749,18 +4295,18 @@
         <v>30</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="0" t="s">
         <v>313</v>
       </c>
-      <c r="B149" s="0" t="s">
+      <c r="B149" s="2" t="s">
         <v>314</v>
       </c>
       <c r="D149" s="0" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="382" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="s">
         <v>315</v>
       </c>
@@ -3771,7 +4317,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="370.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="0" t="s">
         <v>317</v>
       </c>
@@ -3779,14 +4325,14 @@
         <v>318</v>
       </c>
       <c r="D151" s="0" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="152" customFormat="false" ht="370.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="0" t="s">
         <v>319</v>
       </c>
-      <c r="B152" s="2" t="s">
+      <c r="B152" s="0" t="s">
         <v>320</v>
       </c>
       <c r="D152" s="0" t="s">
@@ -3804,18 +4350,18 @@
         <v>81</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="0" t="s">
         <v>323</v>
       </c>
-      <c r="B154" s="0" t="s">
+      <c r="B154" s="2" t="s">
         <v>324</v>
       </c>
       <c r="D154" s="0" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="359" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
         <v>325</v>
       </c>
@@ -3823,14 +4369,14 @@
         <v>326</v>
       </c>
       <c r="D155" s="0" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="370.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="0" t="s">
         <v>327</v>
       </c>
-      <c r="B156" s="2" t="s">
+      <c r="B156" s="0" t="s">
         <v>328</v>
       </c>
       <c r="D156" s="0" t="s">
@@ -3848,18 +4394,18 @@
         <v>91</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="0" t="s">
         <v>331</v>
       </c>
-      <c r="B158" s="0" t="s">
+      <c r="B158" s="2" t="s">
         <v>332</v>
       </c>
       <c r="D158" s="0" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="359" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="117" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="0" t="s">
         <v>333</v>
       </c>
@@ -3867,29 +4413,29 @@
         <v>334</v>
       </c>
       <c r="D159" s="0" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="474" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="117" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="0" t="s">
         <v>335</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D160" s="0" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="451" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="161" customFormat="false" ht="94" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="0" t="s">
         <v>337</v>
       </c>
       <c r="B161" s="2" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="162" customFormat="false" ht="336" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D161" s="0" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="82.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="0" t="s">
         <v>339</v>
       </c>
@@ -3897,40 +4443,40 @@
         <v>340</v>
       </c>
       <c r="D162" s="0" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="163" customFormat="false" ht="324" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="0" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D163" s="0" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="151.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="164" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="0" t="s">
         <v>344</v>
       </c>
-      <c r="B164" s="2" t="s">
+      <c r="B164" s="0" t="s">
         <v>345</v>
+      </c>
+      <c r="C164" s="0" t="s">
+        <v>346</v>
+      </c>
+      <c r="D164" s="0" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="0" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B165" s="0" t="s">
-        <v>347</v>
-      </c>
-      <c r="C165" s="0" t="s">
         <v>348</v>
       </c>
       <c r="D165" s="0" t="s">
-        <v>122</v>
+        <v>276</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3940,87 +4486,818 @@
       <c r="B166" s="0" t="s">
         <v>350</v>
       </c>
-      <c r="D166" s="0" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="167" customFormat="false" ht="531.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="167" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="0" t="s">
         <v>351</v>
       </c>
-      <c r="B167" s="2" t="s">
+      <c r="B167" s="0" t="s">
         <v>352</v>
       </c>
-    </row>
-    <row r="168" customFormat="false" ht="1383" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C167" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D167" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="0" t="s">
         <v>353</v>
       </c>
-      <c r="B168" s="2" t="s">
+      <c r="B168" s="0" t="s">
         <v>354</v>
       </c>
       <c r="C168" s="0" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="169" customFormat="false" ht="945.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="0" t="s">
         <v>355</v>
       </c>
-      <c r="B169" s="2" t="s">
+      <c r="B169" s="0" t="s">
         <v>356</v>
       </c>
       <c r="C169" s="0" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="170" customFormat="false" ht="842" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+      <c r="D169" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="0" t="s">
         <v>357</v>
       </c>
-      <c r="B170" s="2" t="s">
+      <c r="B170" s="0" t="s">
         <v>358</v>
       </c>
-      <c r="C170" s="0" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="171" customFormat="false" ht="773" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D170" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="171" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="0" t="s">
         <v>359</v>
       </c>
-      <c r="B171" s="2" t="s">
+      <c r="B171" s="0" t="s">
         <v>360</v>
       </c>
-      <c r="C171" s="0" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="172" customFormat="false" ht="462.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D171" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="0" t="s">
         <v>361</v>
       </c>
-      <c r="B172" s="2" t="s">
+      <c r="B172" s="0" t="s">
         <v>362</v>
       </c>
       <c r="C172" s="0" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="173" customFormat="false" ht="727" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>6</v>
+      </c>
+      <c r="D172" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="0" t="s">
         <v>363</v>
       </c>
-      <c r="B173" s="2" t="s">
+      <c r="B173" s="0" t="s">
         <v>364</v>
       </c>
-    </row>
-    <row r="174" customFormat="false" ht="2407.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D173" s="0" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="0" t="s">
         <v>365</v>
       </c>
       <c r="B174" s="2" t="s">
         <v>366</v>
+      </c>
+      <c r="D174" s="0" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="0" t="s">
+        <v>367</v>
+      </c>
+      <c r="B175" s="0" t="s">
+        <v>368</v>
+      </c>
+      <c r="C175" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D175" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="176" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A176" s="0" t="s">
+        <v>369</v>
+      </c>
+      <c r="B176" s="0" t="s">
+        <v>370</v>
+      </c>
+      <c r="C176" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D176" s="0" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="177" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A177" s="0" t="s">
+        <v>371</v>
+      </c>
+      <c r="B177" s="0" t="s">
+        <v>372</v>
+      </c>
+      <c r="C177" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D177" s="0" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="178" customFormat="false" ht="151.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A178" s="0" t="s">
+        <v>373</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="C178" s="0" t="s">
+        <v>86</v>
+      </c>
+      <c r="D178" s="0" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="179" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A179" s="0" t="s">
+        <v>375</v>
+      </c>
+      <c r="B179" s="0" t="s">
+        <v>376</v>
+      </c>
+      <c r="C179" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D179" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="180" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A180" s="0" t="s">
+        <v>377</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D180" s="0" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="181" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A181" s="0" t="s">
+        <v>380</v>
+      </c>
+      <c r="B181" s="0" t="s">
+        <v>381</v>
+      </c>
+      <c r="C181" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="D181" s="0" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="182" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A182" s="0" t="s">
+        <v>382</v>
+      </c>
+      <c r="B182" s="0" t="s">
+        <v>383</v>
+      </c>
+      <c r="D182" s="0" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="183" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A183" s="0" t="s">
+        <v>384</v>
+      </c>
+      <c r="B183" s="0" t="s">
+        <v>385</v>
+      </c>
+      <c r="D183" s="0" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="184" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A184" s="0" t="s">
+        <v>386</v>
+      </c>
+      <c r="B184" s="0" t="s">
+        <v>387</v>
+      </c>
+      <c r="C184" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D184" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="185" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A185" s="0" t="s">
+        <v>388</v>
+      </c>
+      <c r="B185" s="0" t="s">
+        <v>389</v>
+      </c>
+      <c r="D185" s="0" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="186" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A186" s="0" t="s">
+        <v>390</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D186" s="0" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="187" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A187" s="0" t="s">
+        <v>392</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D187" s="0" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="188" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A188" s="0" t="s">
+        <v>394</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D188" s="0" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="189" customFormat="false" ht="94" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A189" s="0" t="s">
+        <v>396</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D189" s="0" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="190" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A190" s="0" t="s">
+        <v>398</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="D190" s="0" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="191" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A191" s="0" t="s">
+        <v>400</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D191" s="0" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="192" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A192" s="0" t="s">
+        <v>402</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D192" s="0" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="193" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A193" s="0" t="s">
+        <v>404</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="D193" s="0" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="194" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A194" s="0" t="s">
+        <v>406</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D194" s="0" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="195" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A195" s="0" t="s">
+        <v>408</v>
+      </c>
+      <c r="B195" s="0" t="s">
+        <v>409</v>
+      </c>
+      <c r="D195" s="0" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="196" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A196" s="0" t="s">
+        <v>410</v>
+      </c>
+      <c r="B196" s="0" t="s">
+        <v>411</v>
+      </c>
+      <c r="D196" s="0" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="197" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A197" s="0" t="s">
+        <v>412</v>
+      </c>
+      <c r="B197" s="0" t="s">
+        <v>413</v>
+      </c>
+      <c r="D197" s="0" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="198" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A198" s="0" t="s">
+        <v>414</v>
+      </c>
+      <c r="B198" s="0" t="s">
+        <v>415</v>
+      </c>
+      <c r="D198" s="0" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="199" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A199" s="0" t="s">
+        <v>416</v>
+      </c>
+      <c r="B199" s="0" t="s">
+        <v>417</v>
+      </c>
+      <c r="D199" s="0" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="200" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A200" s="0" t="s">
+        <v>418</v>
+      </c>
+      <c r="B200" s="0" t="s">
+        <v>419</v>
+      </c>
+      <c r="C200" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D200" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="201" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A201" s="0" t="s">
+        <v>420</v>
+      </c>
+      <c r="B201" s="0" t="s">
+        <v>421</v>
+      </c>
+      <c r="D201" s="0" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="202" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A202" s="0" t="s">
+        <v>422</v>
+      </c>
+      <c r="B202" s="0" t="s">
+        <v>423</v>
+      </c>
+      <c r="D202" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="203" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A203" s="0" t="s">
+        <v>424</v>
+      </c>
+      <c r="B203" s="0" t="s">
+        <v>425</v>
+      </c>
+      <c r="C203" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D203" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="204" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A204" s="0" t="s">
+        <v>426</v>
+      </c>
+      <c r="B204" s="0" t="s">
+        <v>427</v>
+      </c>
+      <c r="C204" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="D204" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="205" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A205" s="0" t="s">
+        <v>428</v>
+      </c>
+      <c r="B205" s="0" t="s">
+        <v>429</v>
+      </c>
+      <c r="D205" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="206" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A206" s="0" t="s">
+        <v>430</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D206" s="0" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="207" customFormat="false" ht="94" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A207" s="0" t="s">
+        <v>433</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D207" s="0" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="208" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A208" s="0" t="s">
+        <v>435</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D208" s="0" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="209" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A209" s="0" t="s">
+        <v>437</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="D209" s="0" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="210" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A210" s="0" t="s">
+        <v>439</v>
+      </c>
+      <c r="B210" s="0" t="s">
+        <v>440</v>
+      </c>
+      <c r="D210" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="211" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A211" s="0" t="s">
+        <v>441</v>
+      </c>
+      <c r="B211" s="0" t="s">
+        <v>442</v>
+      </c>
+      <c r="C211" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="D211" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="212" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A212" s="0" t="s">
+        <v>443</v>
+      </c>
+      <c r="B212" s="0" t="s">
+        <v>444</v>
+      </c>
+      <c r="C212" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="D212" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="213" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A213" s="0" t="s">
+        <v>445</v>
+      </c>
+      <c r="B213" s="0" t="s">
+        <v>446</v>
+      </c>
+      <c r="C213" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="D213" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="214" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A214" s="0" t="s">
+        <v>447</v>
+      </c>
+      <c r="B214" s="0" t="s">
+        <v>448</v>
+      </c>
+      <c r="C214" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="D214" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="215" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A215" s="0" t="s">
+        <v>449</v>
+      </c>
+      <c r="B215" s="0" t="s">
+        <v>450</v>
+      </c>
+      <c r="C215" s="0" t="s">
+        <v>346</v>
+      </c>
+      <c r="D215" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="216" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A216" s="0" t="s">
+        <v>451</v>
+      </c>
+      <c r="B216" s="0" t="s">
+        <v>452</v>
+      </c>
+      <c r="C216" s="0" t="s">
+        <v>137</v>
+      </c>
+      <c r="D216" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="217" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A217" s="0" t="s">
+        <v>453</v>
+      </c>
+      <c r="B217" s="0" t="s">
+        <v>454</v>
+      </c>
+      <c r="C217" s="0" t="s">
+        <v>346</v>
+      </c>
+      <c r="D217" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="218" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A218" s="0" t="s">
+        <v>455</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D218" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="219" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A219" s="0" t="s">
+        <v>457</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D219" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="220" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A220" s="0" t="s">
+        <v>459</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D220" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="221" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A221" s="0" t="s">
+        <v>461</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D221" s="0" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="222" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A222" s="0" t="s">
+        <v>463</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="223" customFormat="false" ht="94" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A223" s="0" t="s">
+        <v>465</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="224" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A224" s="0" t="s">
+        <v>467</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="225" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A225" s="0" t="s">
+        <v>469</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="226" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A226" s="0" t="s">
+        <v>471</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="227" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A227" s="0" t="s">
+        <v>473</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="228" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A228" s="0" t="s">
+        <v>475</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="229" customFormat="false" ht="186" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A229" s="0" t="s">
+        <v>477</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="230" customFormat="false" ht="232" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A230" s="0" t="s">
+        <v>479</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="C230" s="0" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="231" customFormat="false" ht="220.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A231" s="0" t="s">
+        <v>481</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="232" customFormat="false" ht="186" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A232" s="0" t="s">
+        <v>483</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C232" s="0" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="233" customFormat="false" ht="174.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A233" s="0" t="s">
+        <v>485</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C233" s="0" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="234" customFormat="false" ht="140" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A234" s="0" t="s">
+        <v>487</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C234" s="0" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="235" customFormat="false" ht="174.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A235" s="0" t="s">
+        <v>489</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="236" customFormat="false" ht="370.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A236" s="0" t="s">
+        <v>491</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="237" customFormat="false" ht="324" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A237" s="0" t="s">
+        <v>493</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="238" customFormat="false" ht="209" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A238" s="0" t="s">
+        <v>495</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>496</v>
       </c>
     </row>
   </sheetData>
@@ -4057,18 +5334,18 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>367</v>
+        <v>497</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>368</v>
+        <v>498</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>369</v>
+        <v>499</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>370</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/DAX_measures_and_user_defined_function.xlsx
+++ b/DAX_measures_and_user_defined_function.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Function" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Measures!$A$1:$D$174</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Measures!$A$1:$D$238</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -1850,7 +1850,7 @@
 RETURN
 "The 9+3 forecast anticipated a €" &amp; FORMAT(ForecastShortfall / 1000, "#,##0") &amp;
 "K gross profit shortfall vs Budget, equal to " &amp; FORMAT([Forecast Captured %], "0%") &amp;
-" of the €" &amp; FORMAT(ActualShortfall / 1000, "#,##0") &amp; "K actual shortfall vs Budget. The remaining €" &amp; FORMAT((ActualShortfall-ForecastShortfall) / 1000, "#,##0") &amp; "K came from two events not known at the time of the forecast (Nov's higher hours per unit and Dec's raw material quality issue) and normal fluctuations."</t>
+" of the €" &amp; FORMAT(ActualShortfall / 1000, "#,##0") &amp; "K actual shortfall vs Budget. The remaining €" &amp; FORMAT((ActualShortfall-ForecastShortfall) / 1000, "#,##0") &amp; "K came from two events not known when the forecast was prepared (Nov's higher hours per unit and Dec's raw material quality issue) and normal fluctuations."</t>
   </si>
   <si>
     <t xml:space="preserve">Gross Profit Variance Check</t>
@@ -2241,8 +2241,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2481,23 +2485,23 @@
   <dimension ref="A1:D238"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46.61"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="147.34"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24.77"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2579,22 +2583,22 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="140" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D8" s="0" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="140" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="3" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="0" t="s">
@@ -2726,33 +2730,33 @@
         <v>30</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="163" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="0" t="s">
         <v>45</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="3" t="s">
         <v>46</v>
       </c>
       <c r="D20" s="0" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="163" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="0" t="s">
         <v>47</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="B21" s="3" t="s">
         <v>48</v>
       </c>
       <c r="D21" s="0" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="163" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="0" t="s">
         <v>49</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="B22" s="3" t="s">
         <v>50</v>
       </c>
       <c r="D22" s="0" t="s">
@@ -2884,22 +2888,22 @@
         <v>62</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="94" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="382" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="0" t="s">
         <v>73</v>
       </c>
-      <c r="B33" s="2" t="s">
+      <c r="B33" s="3" t="s">
         <v>74</v>
       </c>
       <c r="D33" s="0" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="163" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="0" t="s">
         <v>75</v>
       </c>
-      <c r="B34" s="2" t="s">
+      <c r="B34" s="3" t="s">
         <v>76</v>
       </c>
       <c r="D34" s="0" t="s">
@@ -3070,22 +3074,22 @@
         <v>81</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="151.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="451" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="0" t="s">
         <v>106</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B48" s="3" t="s">
         <v>107</v>
       </c>
       <c r="D48" s="0" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="151.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="451" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="0" t="s">
         <v>108</v>
       </c>
-      <c r="B49" s="2" t="s">
+      <c r="B49" s="3" t="s">
         <v>109</v>
       </c>
       <c r="C49" s="0" t="s">
@@ -3095,11 +3099,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="50" customFormat="false" ht="140" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="0" t="s">
         <v>110</v>
       </c>
-      <c r="B50" s="2" t="s">
+      <c r="B50" s="3" t="s">
         <v>111</v>
       </c>
       <c r="D50" s="0" t="s">
@@ -3117,22 +3121,22 @@
         <v>81</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="151.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="0" t="s">
         <v>114</v>
       </c>
-      <c r="B52" s="2" t="s">
+      <c r="B52" s="3" t="s">
         <v>115</v>
       </c>
       <c r="D52" s="0" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="140" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="0" t="s">
         <v>116</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="B53" s="3" t="s">
         <v>117</v>
       </c>
       <c r="D53" s="0" t="s">
@@ -3362,44 +3366,44 @@
         <v>122</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="266.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="0" t="s">
         <v>154</v>
       </c>
-      <c r="B71" s="2" t="s">
+      <c r="B71" s="3" t="s">
         <v>155</v>
       </c>
       <c r="D71" s="0" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="72" customFormat="false" ht="255" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="0" t="s">
         <v>156</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B72" s="3" t="s">
         <v>157</v>
       </c>
       <c r="D72" s="0" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="255" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="0" t="s">
         <v>158</v>
       </c>
-      <c r="B73" s="2" t="s">
+      <c r="B73" s="3" t="s">
         <v>159</v>
       </c>
       <c r="D73" s="0" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="312.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="0" t="s">
         <v>160</v>
       </c>
-      <c r="B74" s="2" t="s">
+      <c r="B74" s="3" t="s">
         <v>161</v>
       </c>
       <c r="D74" s="0" t="s">
@@ -3431,11 +3435,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="255" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="0" t="s">
         <v>166</v>
       </c>
-      <c r="B77" s="2" t="s">
+      <c r="B77" s="3" t="s">
         <v>167</v>
       </c>
       <c r="D77" s="0" t="s">
@@ -3467,11 +3471,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="266.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="0" t="s">
         <v>172</v>
       </c>
-      <c r="B80" s="2" t="s">
+      <c r="B80" s="3" t="s">
         <v>173</v>
       </c>
       <c r="D80" s="0" t="s">
@@ -3497,19 +3501,19 @@
         <v>137</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="94" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="243.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="0" t="s">
         <v>178</v>
       </c>
-      <c r="B83" s="2" t="s">
+      <c r="B83" s="3" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="128.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="84" customFormat="false" ht="382" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="0" t="s">
         <v>180</v>
       </c>
-      <c r="B84" s="2" t="s">
+      <c r="B84" s="3" t="s">
         <v>181</v>
       </c>
       <c r="C84" s="0" t="s">
@@ -3917,66 +3921,66 @@
         <v>91</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="71" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="116" customFormat="false" ht="243.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="0" t="s">
         <v>244</v>
       </c>
-      <c r="B116" s="2" t="s">
+      <c r="B116" s="3" t="s">
         <v>245</v>
       </c>
       <c r="D116" s="0" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="71" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="243.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="0" t="s">
         <v>247</v>
       </c>
-      <c r="B117" s="2" t="s">
+      <c r="B117" s="3" t="s">
         <v>248</v>
       </c>
       <c r="D117" s="0" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="71" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="266.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="0" t="s">
         <v>250</v>
       </c>
-      <c r="B118" s="2" t="s">
+      <c r="B118" s="3" t="s">
         <v>251</v>
       </c>
       <c r="D118" s="0" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="71" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="266.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="0" t="s">
         <v>252</v>
       </c>
-      <c r="B119" s="2" t="s">
+      <c r="B119" s="3" t="s">
         <v>253</v>
       </c>
       <c r="D119" s="0" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="117" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="0" t="s">
         <v>254</v>
       </c>
-      <c r="B120" s="2" t="s">
+      <c r="B120" s="3" t="s">
         <v>255</v>
       </c>
       <c r="D120" s="0" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="71" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="255" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="0" t="s">
         <v>256</v>
       </c>
-      <c r="B121" s="2" t="s">
+      <c r="B121" s="3" t="s">
         <v>257</v>
       </c>
       <c r="C121" s="0" t="s">
@@ -3986,11 +3990,11 @@
         <v>246</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="71" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="255" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="0" t="s">
         <v>258</v>
       </c>
-      <c r="B122" s="2" t="s">
+      <c r="B122" s="3" t="s">
         <v>259</v>
       </c>
       <c r="C122" s="0" t="s">
@@ -4044,44 +4048,44 @@
         <v>249</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="71" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="255" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="0" t="s">
         <v>268</v>
       </c>
-      <c r="B127" s="2" t="s">
+      <c r="B127" s="3" t="s">
         <v>269</v>
       </c>
       <c r="D127" s="0" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="71" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="255" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="0" t="s">
         <v>270</v>
       </c>
-      <c r="B128" s="2" t="s">
+      <c r="B128" s="3" t="s">
         <v>271</v>
       </c>
       <c r="D128" s="0" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="692.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="0" t="s">
         <v>272</v>
       </c>
-      <c r="B129" s="2" t="s">
+      <c r="B129" s="3" t="s">
         <v>273</v>
       </c>
       <c r="D129" s="0" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="209" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="0" t="s">
         <v>274</v>
       </c>
-      <c r="B130" s="2" t="s">
+      <c r="B130" s="3" t="s">
         <v>275</v>
       </c>
       <c r="D130" s="0" t="s">
@@ -4102,33 +4106,33 @@
         <v>276</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="209" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="0" t="s">
         <v>279</v>
       </c>
-      <c r="B132" s="2" t="s">
+      <c r="B132" s="3" t="s">
         <v>280</v>
       </c>
       <c r="D132" s="0" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="151.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="451" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="0" t="s">
         <v>281</v>
       </c>
-      <c r="B133" s="2" t="s">
+      <c r="B133" s="3" t="s">
         <v>282</v>
       </c>
       <c r="D133" s="0" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="140" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="134" customFormat="false" ht="439.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="0" t="s">
         <v>283</v>
       </c>
-      <c r="B134" s="2" t="s">
+      <c r="B134" s="3" t="s">
         <v>284</v>
       </c>
       <c r="D134" s="0" t="s">
@@ -4163,33 +4167,33 @@
         <v>276</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="140" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="0" t="s">
         <v>289</v>
       </c>
-      <c r="B137" s="2" t="s">
+      <c r="B137" s="3" t="s">
         <v>290</v>
       </c>
       <c r="D137" s="0" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="151.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="0" t="s">
         <v>291</v>
       </c>
-      <c r="B138" s="2" t="s">
+      <c r="B138" s="3" t="s">
         <v>292</v>
       </c>
       <c r="D138" s="0" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="94" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="382" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="0" t="s">
         <v>293</v>
       </c>
-      <c r="B139" s="2" t="s">
+      <c r="B139" s="3" t="s">
         <v>294</v>
       </c>
       <c r="D139" s="0" t="s">
@@ -4218,22 +4222,22 @@
         <v>62</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="142" customFormat="false" ht="266.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="0" t="s">
         <v>299</v>
       </c>
-      <c r="B142" s="2" t="s">
+      <c r="B142" s="3" t="s">
         <v>300</v>
       </c>
       <c r="D142" s="0" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="266.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="0" t="s">
         <v>301</v>
       </c>
-      <c r="B143" s="2" t="s">
+      <c r="B143" s="3" t="s">
         <v>302</v>
       </c>
       <c r="D143" s="0" t="s">
@@ -4262,11 +4266,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="266.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="0" t="s">
         <v>307</v>
       </c>
-      <c r="B146" s="2" t="s">
+      <c r="B146" s="3" t="s">
         <v>308</v>
       </c>
       <c r="D146" s="0" t="s">
@@ -4295,33 +4299,33 @@
         <v>30</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="149" customFormat="false" ht="266.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="0" t="s">
         <v>313</v>
       </c>
-      <c r="B149" s="2" t="s">
+      <c r="B149" s="3" t="s">
         <v>314</v>
       </c>
       <c r="D149" s="0" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="255" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="0" t="s">
         <v>315</v>
       </c>
-      <c r="B150" s="2" t="s">
+      <c r="B150" s="3" t="s">
         <v>316</v>
       </c>
       <c r="D150" s="0" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="255" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="0" t="s">
         <v>317</v>
       </c>
-      <c r="B151" s="2" t="s">
+      <c r="B151" s="3" t="s">
         <v>318</v>
       </c>
       <c r="D151" s="0" t="s">
@@ -4350,22 +4354,22 @@
         <v>81</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="154" customFormat="false" ht="255" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="0" t="s">
         <v>323</v>
       </c>
-      <c r="B154" s="2" t="s">
+      <c r="B154" s="3" t="s">
         <v>324</v>
       </c>
       <c r="D154" s="0" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="255" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="0" t="s">
         <v>325</v>
       </c>
-      <c r="B155" s="2" t="s">
+      <c r="B155" s="3" t="s">
         <v>326</v>
       </c>
       <c r="D155" s="0" t="s">
@@ -4394,63 +4398,63 @@
         <v>91</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="255" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="0" t="s">
         <v>331</v>
       </c>
-      <c r="B158" s="2" t="s">
+      <c r="B158" s="3" t="s">
         <v>332</v>
       </c>
       <c r="D158" s="0" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="117" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="370.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="0" t="s">
         <v>333</v>
       </c>
-      <c r="B159" s="2" t="s">
+      <c r="B159" s="3" t="s">
         <v>334</v>
       </c>
       <c r="D159" s="0" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="117" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="160" customFormat="false" ht="370.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="0" t="s">
         <v>335</v>
       </c>
-      <c r="B160" s="2" t="s">
+      <c r="B160" s="3" t="s">
         <v>336</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="94" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="161" customFormat="false" ht="289.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="0" t="s">
         <v>337</v>
       </c>
-      <c r="B161" s="2" t="s">
+      <c r="B161" s="3" t="s">
         <v>338</v>
       </c>
       <c r="D161" s="0" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="82.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="278" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="0" t="s">
         <v>339</v>
       </c>
-      <c r="B162" s="2" t="s">
+      <c r="B162" s="3" t="s">
         <v>340</v>
       </c>
       <c r="D162" s="0" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="163" customFormat="false" ht="128.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="0" t="s">
         <v>342</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="B163" s="3" t="s">
         <v>343</v>
       </c>
     </row>
@@ -4573,11 +4577,11 @@
         <v>30</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="174" customFormat="false" ht="220.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="0" t="s">
         <v>365</v>
       </c>
-      <c r="B174" s="2" t="s">
+      <c r="B174" s="3" t="s">
         <v>366</v>
       </c>
       <c r="D174" s="0" t="s">
@@ -4626,11 +4630,11 @@
         <v>91</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="151.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="178" customFormat="false" ht="462.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="0" t="s">
         <v>373</v>
       </c>
-      <c r="B178" s="2" t="s">
+      <c r="B178" s="3" t="s">
         <v>374</v>
       </c>
       <c r="C178" s="0" t="s">
@@ -4654,11 +4658,11 @@
         <v>12</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="180" customFormat="false" ht="140" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="0" t="s">
         <v>377</v>
       </c>
-      <c r="B180" s="2" t="s">
+      <c r="B180" s="3" t="s">
         <v>378</v>
       </c>
       <c r="D180" s="0" t="s">
@@ -4726,99 +4730,99 @@
         <v>81</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="186" customFormat="false" ht="151.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="0" t="s">
         <v>390</v>
       </c>
-      <c r="B186" s="2" t="s">
+      <c r="B186" s="3" t="s">
         <v>391</v>
       </c>
       <c r="D186" s="0" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="187" customFormat="false" ht="163" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="0" t="s">
         <v>392</v>
       </c>
-      <c r="B187" s="2" t="s">
+      <c r="B187" s="3" t="s">
         <v>393</v>
       </c>
       <c r="D187" s="0" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="188" customFormat="false" ht="140" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="0" t="s">
         <v>394</v>
       </c>
-      <c r="B188" s="2" t="s">
+      <c r="B188" s="3" t="s">
         <v>395</v>
       </c>
       <c r="D188" s="0" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="94" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="189" customFormat="false" ht="416.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="0" t="s">
         <v>396</v>
       </c>
-      <c r="B189" s="2" t="s">
+      <c r="B189" s="3" t="s">
         <v>397</v>
       </c>
       <c r="D189" s="0" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="190" customFormat="false" ht="163" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A190" s="0" t="s">
         <v>398</v>
       </c>
-      <c r="B190" s="2" t="s">
+      <c r="B190" s="3" t="s">
         <v>399</v>
       </c>
       <c r="D190" s="0" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="191" customFormat="false" ht="163" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A191" s="0" t="s">
         <v>400</v>
       </c>
-      <c r="B191" s="2" t="s">
+      <c r="B191" s="3" t="s">
         <v>401</v>
       </c>
       <c r="D191" s="0" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="192" customFormat="false" ht="163" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="0" t="s">
         <v>402</v>
       </c>
-      <c r="B192" s="2" t="s">
+      <c r="B192" s="3" t="s">
         <v>403</v>
       </c>
       <c r="D192" s="0" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="193" customFormat="false" ht="140" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="0" t="s">
         <v>404</v>
       </c>
-      <c r="B193" s="2" t="s">
+      <c r="B193" s="3" t="s">
         <v>405</v>
       </c>
       <c r="D193" s="0" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="194" customFormat="false" ht="140" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="0" t="s">
         <v>406</v>
       </c>
-      <c r="B194" s="2" t="s">
+      <c r="B194" s="3" t="s">
         <v>407</v>
       </c>
       <c r="D194" s="0" t="s">
@@ -4955,44 +4959,44 @@
         <v>122</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="206" customFormat="false" ht="174.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="0" t="s">
         <v>430</v>
       </c>
-      <c r="B206" s="2" t="s">
+      <c r="B206" s="3" t="s">
         <v>431</v>
       </c>
       <c r="D206" s="0" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="94" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="207" customFormat="false" ht="382" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A207" s="0" t="s">
         <v>433</v>
       </c>
-      <c r="B207" s="2" t="s">
+      <c r="B207" s="3" t="s">
         <v>434</v>
       </c>
       <c r="D207" s="0" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="208" customFormat="false" ht="140" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="0" t="s">
         <v>435</v>
       </c>
-      <c r="B208" s="2" t="s">
+      <c r="B208" s="3" t="s">
         <v>436</v>
       </c>
       <c r="D208" s="0" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="48" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="209" customFormat="false" ht="163" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A209" s="0" t="s">
         <v>437</v>
       </c>
-      <c r="B209" s="2" t="s">
+      <c r="B209" s="3" t="s">
         <v>438</v>
       </c>
       <c r="D209" s="0" t="s">
@@ -5108,200 +5112,200 @@
         <v>122</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="218" customFormat="false" ht="336" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="0" t="s">
         <v>455</v>
       </c>
-      <c r="B218" s="2" t="s">
+      <c r="B218" s="3" t="s">
         <v>456</v>
       </c>
       <c r="D218" s="0" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="219" customFormat="false" ht="336" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="0" t="s">
         <v>457</v>
       </c>
-      <c r="B219" s="2" t="s">
+      <c r="B219" s="3" t="s">
         <v>458</v>
       </c>
       <c r="D219" s="0" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="220" customFormat="false" ht="278" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="0" t="s">
         <v>459</v>
       </c>
-      <c r="B220" s="2" t="s">
+      <c r="B220" s="3" t="s">
         <v>460</v>
       </c>
       <c r="D220" s="0" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="221" customFormat="false" ht="278" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A221" s="0" t="s">
         <v>461</v>
       </c>
-      <c r="B221" s="2" t="s">
+      <c r="B221" s="3" t="s">
         <v>462</v>
       </c>
       <c r="D221" s="0" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="222" customFormat="false" ht="94" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A222" s="0" t="s">
         <v>463</v>
       </c>
-      <c r="B222" s="2" t="s">
+      <c r="B222" s="3" t="s">
         <v>464</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="94" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="223" customFormat="false" ht="692.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A223" s="0" t="s">
         <v>465</v>
       </c>
-      <c r="B223" s="2" t="s">
+      <c r="B223" s="3" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="224" customFormat="false" ht="209" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="0" t="s">
         <v>467</v>
       </c>
-      <c r="B224" s="2" t="s">
+      <c r="B224" s="3" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" customFormat="false" ht="186" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="0" t="s">
         <v>469</v>
       </c>
-      <c r="B225" s="2" t="s">
+      <c r="B225" s="3" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="59.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" customFormat="false" ht="151.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="0" t="s">
         <v>471</v>
       </c>
-      <c r="B226" s="2" t="s">
+      <c r="B226" s="3" t="s">
         <v>472</v>
       </c>
     </row>
-    <row r="227" customFormat="false" ht="36.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="227" customFormat="false" ht="255" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="0" t="s">
         <v>473</v>
       </c>
-      <c r="B227" s="2" t="s">
+      <c r="B227" s="3" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="228" customFormat="false" ht="105.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="228" customFormat="false" ht="692.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="0" t="s">
         <v>475</v>
       </c>
-      <c r="B228" s="2" t="s">
+      <c r="B228" s="3" t="s">
         <v>476</v>
       </c>
     </row>
-    <row r="229" customFormat="false" ht="186" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="229" customFormat="false" ht="416.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="0" t="s">
         <v>477</v>
       </c>
-      <c r="B229" s="2" t="s">
+      <c r="B229" s="3" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="230" customFormat="false" ht="232" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="230" customFormat="false" ht="520" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A230" s="0" t="s">
         <v>479</v>
       </c>
-      <c r="B230" s="2" t="s">
+      <c r="B230" s="3" t="s">
         <v>480</v>
       </c>
       <c r="C230" s="0" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="231" customFormat="false" ht="220.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="231" customFormat="false" ht="681" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="0" t="s">
         <v>481</v>
       </c>
-      <c r="B231" s="2" t="s">
+      <c r="B231" s="3" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="232" customFormat="false" ht="186" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="232" customFormat="false" ht="577.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="0" t="s">
         <v>483</v>
       </c>
-      <c r="B232" s="2" t="s">
+      <c r="B232" s="3" t="s">
         <v>484</v>
       </c>
       <c r="C232" s="0" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="233" customFormat="false" ht="174.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="233" customFormat="false" ht="554.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="0" t="s">
         <v>485</v>
       </c>
-      <c r="B233" s="2" t="s">
+      <c r="B233" s="3" t="s">
         <v>486</v>
       </c>
       <c r="C233" s="0" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="234" customFormat="false" ht="140" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="234" customFormat="false" ht="347.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="0" t="s">
         <v>487</v>
       </c>
-      <c r="B234" s="2" t="s">
+      <c r="B234" s="3" t="s">
         <v>488</v>
       </c>
       <c r="C234" s="0" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="235" customFormat="false" ht="174.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="235" customFormat="false" ht="554.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="0" t="s">
         <v>489</v>
       </c>
-      <c r="B235" s="2" t="s">
+      <c r="B235" s="3" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="236" customFormat="false" ht="370.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="236" customFormat="false" ht="1671" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="0" t="s">
         <v>491</v>
       </c>
-      <c r="B236" s="2" t="s">
+      <c r="B236" s="3" t="s">
         <v>492</v>
       </c>
     </row>
-    <row r="237" customFormat="false" ht="324" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="237" customFormat="false" ht="1590" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A237" s="0" t="s">
         <v>493</v>
       </c>
-      <c r="B237" s="2" t="s">
+      <c r="B237" s="3" t="s">
         <v>494</v>
       </c>
     </row>
-    <row r="238" customFormat="false" ht="209" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="238" customFormat="false" ht="761.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="0" t="s">
         <v>495</v>
       </c>
-      <c r="B238" s="2" t="s">
+      <c r="B238" s="3" t="s">
         <v>496</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D174"/>
+  <autoFilter ref="A1:D238"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5321,30 +5325,30 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="3" width="13.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="3" width="105.09"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="3" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="4" width="13.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="4" width="105.09"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="4" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="4" t="s">
         <v>497</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>500</v>
       </c>
     </row>
